--- a/data/raw/benv_exports/leucosi_bovina_enzootica_2026_italia.xlsx
+++ b/data/raw/benv_exports/leucosi_bovina_enzootica_2026_italia.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>85268</v>
+        <v>85529</v>
       </c>
       <c r="B2" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -423,10 +423,10 @@
         <v>C</v>
       </c>
       <c r="D2" t="str">
-        <v>22/06/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="E2" t="str">
-        <v>10/06/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="F2" t="str">
         <v>-</v>
@@ -438,7 +438,7 @@
         <v>BOVINO</v>
       </c>
       <c r="I2" t="str">
-        <v>SAN MARCO IN LAMIS</v>
+        <v>LESINA</v>
       </c>
       <c r="J2" t="str">
         <v>FG</v>
@@ -449,7 +449,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>84298</v>
+        <v>85268</v>
       </c>
       <c r="B3" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -458,10 +458,10 @@
         <v>C</v>
       </c>
       <c r="D3" t="str">
-        <v>27/04/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="E3" t="str">
-        <v>20/04/2026</v>
+        <v>10/06/2026</v>
       </c>
       <c r="F3" t="str">
         <v>-</v>
@@ -473,18 +473,53 @@
         <v>BOVINO</v>
       </c>
       <c r="I3" t="str">
+        <v>SAN MARCO IN LAMIS</v>
+      </c>
+      <c r="J3" t="str">
+        <v>FG</v>
+      </c>
+      <c r="K3" t="str">
+        <v>PUGLIA</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>84298</v>
+      </c>
+      <c r="B4" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C4" t="str">
+        <v>C</v>
+      </c>
+      <c r="D4" t="str">
+        <v>27/04/2026</v>
+      </c>
+      <c r="E4" t="str">
+        <v>20/04/2026</v>
+      </c>
+      <c r="F4" t="str">
+        <v>-</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>BOVINO</v>
+      </c>
+      <c r="I4" t="str">
         <v>TREIA</v>
       </c>
-      <c r="J3" t="str">
+      <c r="J4" t="str">
         <v>MC</v>
       </c>
-      <c r="K3" t="str">
+      <c r="K4" t="str">
         <v>MARCHE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
   </ignoredErrors>
 </worksheet>
 </file>